--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20211.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="36">
   <si>
     <t>Mat</t>
   </si>
@@ -82,67 +82,49 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
+    <t>LICEA</t>
+  </si>
+  <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
     <t>HERAS</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>ALDUCIN</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
     <t>CABRERA</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>EDITH</t>
-  </si>
-  <si>
     <t>YADIRA</t>
   </si>
   <si>
+    <t>QADMIEL TAMARA</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>BRENDA JANET</t>
+  </si>
+  <si>
     <t>CESAR ENRIQUE</t>
-  </si>
-  <si>
-    <t>BRENDA JANET</t>
-  </si>
-  <si>
-    <t>LAISHA STEFANY</t>
-  </si>
-  <si>
-    <t>YATZIRI NAOMI</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
   </si>
 </sst>
 </file>
@@ -543,10 +525,10 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2">
         <v>19</v>
@@ -555,7 +537,7 @@
         <v>73.08</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -569,19 +551,19 @@
         <v>23</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>91.3</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -621,19 +603,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>78.13</v>
+        <v>81.25</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -647,19 +629,19 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <v>5</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>63.16</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -673,16 +655,16 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>4</v>
       </c>
       <c r="F7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G7">
-        <v>72.22</v>
+        <v>75</v>
       </c>
       <c r="H7">
         <v>7.8</v>
@@ -738,16 +720,19 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>80.77</v>
+      </c>
+      <c r="H2">
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -761,16 +746,19 @@
         <v>23</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>95.65000000000001</v>
+      </c>
+      <c r="H3">
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -784,16 +772,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>33</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>97.06</v>
+      </c>
+      <c r="H4">
+        <v>8.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -807,16 +798,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
         <v>29</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>90.63</v>
+      </c>
+      <c r="H5">
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -830,16 +824,19 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E6">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>60.53</v>
+      </c>
+      <c r="H6">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -853,16 +850,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>77.78</v>
+      </c>
+      <c r="H7">
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -915,19 +915,19 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>73.08</v>
+        <v>80.77</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -941,19 +941,19 @@
         <v>23</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>91.3</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -970,16 +970,16 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="H4">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -993,19 +993,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G5">
-        <v>78.13</v>
+        <v>90.63</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1019,10 +1019,10 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6">
         <v>24</v>
@@ -1031,7 +1031,7 @@
         <v>63.16</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1045,19 +1045,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G7">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -1067,7 +1067,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1099,16 +1099,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>18330051920242</v>
+        <v>18330051920346</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1117,53 +1117,53 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>18330051920346</v>
+        <v>19330051920237</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920235</v>
+        <v>19330051920366</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1174,10 +1174,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1186,76 +1186,30 @@
         <v>12</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920301</v>
+        <v>19330051920235</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920125</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920398</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20211.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20211.xlsx
@@ -1140,7 +1140,7 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1186,7 +1186,7 @@
         <v>12</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1209,7 +1209,7 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20211.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -85,46 +85,28 @@
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>LICEA</t>
-  </si>
-  <si>
-    <t>CRISTOBAL</t>
+    <t>HERAS</t>
   </si>
   <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>HERAS</t>
-  </si>
-  <si>
     <t>CABRERA</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>BRUNO</t>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>SEGURA</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>YADIRA</t>
   </si>
   <si>
-    <t>QADMIEL TAMARA</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
+    <t>CESAR ENRIQUE</t>
   </si>
   <si>
     <t>BRENDA JANET</t>
-  </si>
-  <si>
-    <t>CESAR ENRIQUE</t>
   </si>
 </sst>
 </file>
@@ -629,16 +611,16 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>5</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6">
-        <v>65.79000000000001</v>
+        <v>68.42</v>
       </c>
       <c r="H6">
         <v>8</v>
@@ -827,7 +809,7 @@
         <v>10</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>23</v>
@@ -1019,19 +1001,19 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>6</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>63.16</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1067,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1105,10 +1087,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1122,16 +1104,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920237</v>
+        <v>19330051920235</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1140,76 +1122,30 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920366</v>
+        <v>19330051920268</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920268</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920235</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20211.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20211.xlsx
@@ -637,10 +637,10 @@
         <v>36</v>
       </c>
       <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7">
         <v>5</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
       </c>
       <c r="F7">
         <v>27</v>
@@ -649,7 +649,7 @@
         <v>75</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
         <v>6</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7">
         <v>28</v>
@@ -1027,10 +1027,10 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7">
         <v>28</v>
@@ -1039,7 +1039,7 @@
         <v>77.78</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20211.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20211.xlsx
@@ -82,31 +82,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>HERAS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>YADIRA</t>
-  </si>
-  <si>
-    <t>CESAR ENRIQUE</t>
-  </si>
-  <si>
-    <t>BRENDA JANET</t>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>AMYRA NAHOMY</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>ESDRAS ALAN</t>
   </si>
 </sst>
 </file>
@@ -507,10 +507,10 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2">
         <v>19</v>
@@ -533,10 +533,10 @@
         <v>23</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>1</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
       </c>
       <c r="F3">
         <v>22</v>
@@ -545,7 +545,7 @@
         <v>95.65000000000001</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -559,10 +559,10 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <v>32</v>
@@ -571,7 +571,7 @@
         <v>94.12</v>
       </c>
       <c r="H4">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -585,19 +585,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>81.25</v>
+        <v>84.38</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -611,10 +611,10 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F6">
         <v>26</v>
@@ -623,7 +623,7 @@
         <v>68.42</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -637,19 +637,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G7">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -702,10 +702,10 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2">
         <v>21</v>
@@ -728,10 +728,10 @@
         <v>23</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>1</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
       </c>
       <c r="F3">
         <v>22</v>
@@ -740,7 +740,7 @@
         <v>95.65000000000001</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -754,10 +754,10 @@
         <v>34</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>1</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>33</v>
@@ -766,7 +766,7 @@
         <v>97.06</v>
       </c>
       <c r="H4">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -780,19 +780,19 @@
         <v>32</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>2</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
       <c r="F5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>90.63</v>
+        <v>93.75</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -806,10 +806,10 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F6">
         <v>23</v>
@@ -818,7 +818,7 @@
         <v>60.53</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -832,19 +832,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>77.78</v>
+        <v>80.56</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -897,19 +897,19 @@
         <v>26</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
       <c r="F2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>80.77</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -923,10 +923,10 @@
         <v>23</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>1</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
       </c>
       <c r="F3">
         <v>22</v>
@@ -935,7 +935,7 @@
         <v>95.65000000000001</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -949,10 +949,10 @@
         <v>34</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>1</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>33</v>
@@ -961,7 +961,7 @@
         <v>97.06</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -975,10 +975,10 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5">
         <v>29</v>
@@ -987,7 +987,7 @@
         <v>90.63</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1001,19 +1001,19 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>65.79000000000001</v>
+        <v>60.53</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1027,19 +1027,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>77.78</v>
+        <v>80.56</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>18330051920346</v>
+        <v>19330051920360</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
@@ -1096,7 +1096,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1104,7 +1104,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920235</v>
+        <v>19330051920366</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -1119,7 +1119,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920268</v>
+        <v>19330051920273</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20211.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -85,28 +85,37 @@
     <t>BRETON</t>
   </si>
   <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
     <t>CRISTOBAL</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
     <t>VICENTE</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
     <t>BRUNO</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
     <t>AMYRA NAHOMY</t>
   </si>
   <si>
+    <t>ASTRID</t>
+  </si>
+  <si>
+    <t>ESDRAS ALAN</t>
+  </si>
+  <si>
     <t>DANIELA</t>
-  </si>
-  <si>
-    <t>ESDRAS ALAN</t>
   </si>
 </sst>
 </file>
@@ -832,19 +841,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>80.56</v>
+        <v>83.33</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -1049,7 +1058,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1087,10 +1096,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1104,16 +1113,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920366</v>
+        <v>19330051920436</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1133,10 +1142,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1145,6 +1154,29 @@
         <v>12</v>
       </c>
       <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>19330051920366</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
     </row>
